--- a/vignettes/data/source_tables/SupplData_MultiTissueImmuneAging_MetadataMappings.xlsx
+++ b/vignettes/data/source_tables/SupplData_MultiTissueImmuneAging_MetadataMappings.xlsx
@@ -381,7 +381,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Metadata mappings and transformations used for the manuscript A multi-tissue map of human immune aging_2026</t>
+          <t>Metadata mappings and transformations used for A multi-tissue immune map across 4,240 single-cell donors resolves asynchronous immune ageing</t>
         </is>
       </c>
     </row>
@@ -412,12 +412,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Manuscript document</t>
+          <t>Analysis repository</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://docs.google.com/document/d/1Ri2Dyr4Rhv1rvgIXeUm5NI27IrdPKJS1jI2J-SJjk9I</t>
+          <t>https://github.com/MangiolaLaboratory/immuneHealthyBodyMap</t>
         </is>
       </c>
     </row>
@@ -429,7 +429,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/home/a1237163/lab/chen/HPC_posterior/TAR_SCRIPTS/functions/edit_covariates.R</t>
+          <t>vignettes/targets_pipeline/functions/edit_covariates.R</t>
         </is>
       </c>
     </row>
@@ -441,7 +441,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>e844a8eb201d4dfe04aca1dccb89097a</t>
+          <t>456c4044e9c59b7bda1f8fc3689c44a9</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/hpcfs/groups/phoenix-hpc-mangiola_laboratory/Mangiola_ImmuneAtlas/disease_data_grouped_further.csv</t>
+          <t>vignettes/data/source_tables/disease_data_grouped_further.csv</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
